--- a/Exp3_PTO_GRPO/eda/results/all/tables/6_stats/6_stats.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/all/tables/6_stats/6_stats.xlsx
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.71</v>
+        <v>2.858</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.609</v>
+        <v>0.622</v>
       </c>
       <c r="G5" t="n">
-        <v>0.592</v>
+        <v>0.658</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -688,16 +688,16 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.413</v>
+        <v>0.439</v>
       </c>
       <c r="K5" t="n">
         <v>0.8159999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.104</v>
+        <v>0.103</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0396</v>
+        <v>0.0401</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1136,16 +1136,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.691</v>
+        <v>2.837</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>0.845</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.954</v>
+        <v>0.899</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1156,16 +1156,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.66</v>
+        <v>0.637</v>
       </c>
       <c r="K14" t="n">
-        <v>1.023</v>
+        <v>0.997</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0885</v>
+        <v>0.0818</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.675</v>
+        <v>2.839</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>0.547</v>
+        <v>0.523</v>
       </c>
       <c r="G23" t="n">
-        <v>0.494</v>
+        <v>0.483</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1624,16 +1624,16 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.328</v>
+        <v>0.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.766</v>
+        <v>0.729</v>
       </c>
       <c r="L23" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1408</v>
+        <v>0.1373</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.71</v>
+        <v>2.858</v>
       </c>
       <c r="E32" t="n">
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>0.616</v>
+        <v>0.583</v>
       </c>
       <c r="G32" t="n">
-        <v>0.767</v>
+        <v>0.716</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2092,16 +2092,16 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.463</v>
+        <v>0.425</v>
       </c>
       <c r="K32" t="n">
-        <v>0.778</v>
+        <v>0.753</v>
       </c>
       <c r="L32" t="n">
-        <v>0.104</v>
+        <v>0.103</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0396</v>
+        <v>0.0401</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2540,16 +2540,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2.691</v>
+        <v>2.837</v>
       </c>
       <c r="E41" t="n">
         <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>0.845</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>0.954</v>
+        <v>0.899</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.66</v>
+        <v>0.637</v>
       </c>
       <c r="K41" t="n">
-        <v>1.023</v>
+        <v>0.997</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0885</v>
+        <v>0.0818</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3008,16 +3008,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.675</v>
+        <v>2.839</v>
       </c>
       <c r="E50" t="n">
         <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>0.547</v>
+        <v>0.523</v>
       </c>
       <c r="G50" t="n">
-        <v>0.494</v>
+        <v>0.483</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3028,16 +3028,16 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.328</v>
+        <v>0.3</v>
       </c>
       <c r="K50" t="n">
-        <v>0.766</v>
+        <v>0.729</v>
       </c>
       <c r="L50" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1408</v>
+        <v>0.1373</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>129.4716</v>
+        <v>129.3604</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1349</v>
+        <v>0.1348</v>
       </c>
       <c r="F5" t="n">
         <v>11</v>
@@ -3690,13 +3690,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>191.6901</v>
+        <v>183.4767</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1997</v>
+        <v>0.1911</v>
       </c>
       <c r="F14" t="n">
         <v>11</v>
@@ -3933,13 +3933,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37.167</v>
+        <v>41.5716</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0968</v>
+        <v>0.1083</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -5030,13 +5030,13 @@
         <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1372</v>
+        <v>-0.0799</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1481</v>
+        <v>-0.0935</v>
       </c>
       <c r="G5" t="n">
-        <v>0.657</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5255,10 +5255,10 @@
         <v>96</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0017</v>
+        <v>0.0156</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0018</v>
+        <v>0.0154</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -5461,7 +5461,7 @@
         <v>-0.22</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1791</v>
+        <v>0.1538</v>
       </c>
     </row>
     <row r="23">
@@ -5480,13 +5480,13 @@
         <v>96</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2118</v>
+        <v>-0.184</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2455</v>
+        <v>-0.2371</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1791</v>
+        <v>0.1277</v>
       </c>
     </row>
     <row r="24">
@@ -5611,7 +5611,7 @@
         <v>-0.242</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1791</v>
+        <v>0.1538</v>
       </c>
     </row>
     <row r="29">
@@ -5705,10 +5705,10 @@
         <v>96</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0556</v>
+        <v>-0.0313</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0413</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -5930,10 +5930,10 @@
         <v>96</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0486</v>
+        <v>0.0503</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0593</v>
+        <v>0.0623</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -6086,7 +6086,7 @@
         <v>0.3238</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0786</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="48">
@@ -6136,7 +6136,7 @@
         <v>0.1972</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2856</v>
+        <v>0.2609</v>
       </c>
     </row>
     <row r="50">
@@ -6155,13 +6155,13 @@
         <v>96</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1406</v>
+        <v>0.224</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1863</v>
+        <v>0.3042</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2856</v>
+        <v>0.0346</v>
       </c>
     </row>
     <row r="51">
@@ -6236,7 +6236,7 @@
         <v>0.2465</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0987</v>
+        <v>0.08459999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -6286,7 +6286,7 @@
         <v>0.2736</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1419</v>
+        <v>0.1183</v>
       </c>
     </row>
     <row r="56">
@@ -6380,10 +6380,10 @@
         <v>96</v>
       </c>
       <c r="E59" t="n">
-        <v>0.033</v>
+        <v>0.0278</v>
       </c>
       <c r="F59" t="n">
-        <v>0.038</v>
+        <v>0.0334</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -6605,13 +6605,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1024</v>
+        <v>0.1128</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1293</v>
+        <v>0.1558</v>
       </c>
       <c r="G68" t="n">
-        <v>0.4445</v>
+        <v>0.2233</v>
       </c>
     </row>
     <row r="69">
@@ -6736,7 +6736,7 @@
         <v>0.2577</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2999</v>
+        <v>0.2399</v>
       </c>
     </row>
     <row r="74">
@@ -6830,10 +6830,10 @@
         <v>96</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6632</v>
+        <v>0.5833</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8349</v>
+        <v>0.7663</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -7055,10 +7055,10 @@
         <v>96</v>
       </c>
       <c r="E86" t="n">
-        <v>0.217</v>
+        <v>0.1736</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2817</v>
+        <v>0.2668</v>
       </c>
       <c r="G86" t="n">
         <v>0.0146</v>
@@ -7280,10 +7280,10 @@
         <v>96</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0174</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F95" t="n">
-        <v>0.017</v>
+        <v>-0.0091</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.0747</v>
+        <v>-0.0312</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0789</v>
+        <v>-0.0342</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.0295</v>
+        <v>-0.0174</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0311</v>
+        <v>-0.0192</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -7979,10 +7979,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.0208</v>
+        <v>-0.0243</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0242</v>
+        <v>-0.0298</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-0.0122</v>
+        <v>0.0174</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0152</v>
+        <v>0.0241</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -8411,10 +8411,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.0799</v>
+        <v>0.0399</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0867</v>
+        <v>0.0445</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
@@ -8670,13 +8670,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1044</v>
+        <v>0.1032</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0396</v>
+        <v>0.0401</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
@@ -8886,13 +8886,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1995</v>
+        <v>0.1879</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0885</v>
+        <v>0.0818</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
@@ -9102,10 +9102,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1412</v>
+        <v>0.1416</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1408</v>
+        <v>0.1373</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="4">
@@ -9287,7 +9287,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="5">
@@ -9297,7 +9297,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
     </row>
   </sheetData>
